--- a/output/model_analysis_20260429/model_bin_user_profile_pivot.xlsx
+++ b/output/model_analysis_20260429/model_bin_user_profile_pivot.xlsx
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,13 +37,26 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="00333333"/>
     </font>
     <font>
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -52,7 +65,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F6F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -87,38 +105,50 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1297,7 +1327,7 @@
       <c r="F6" s="6" t="n">
         <v>34.05555555555556</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="8" t="n">
         <v>37.81818181818182</v>
       </c>
     </row>
@@ -1441,7 +1471,7 @@
       <c r="F14" s="6" t="n">
         <v>0.3888888888888889</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="8" t="n">
         <v>0.3838383838383838</v>
       </c>
     </row>
@@ -1485,7 +1515,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>state_cnt</t>
         </is>
@@ -1539,25 +1569,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="9" t="n">
+      <c r="F3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="11" t="n">
         <v>36</v>
       </c>
     </row>
@@ -1567,25 +1597,25 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="9" t="n">
+      <c r="G4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="11" t="n">
         <v>40</v>
       </c>
     </row>
@@ -1595,25 +1625,25 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="9" t="n">
+      <c r="F5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="11" t="n">
         <v>23</v>
       </c>
     </row>
@@ -1623,32 +1653,32 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="9" t="n">
+      <c r="H6" s="12" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="7"/>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>state_pct</t>
         </is>
@@ -1702,25 +1732,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="13" t="n">
         <v>0.3611111111111111</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="13" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="13" t="n">
         <v>0.2222222222222222</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="13" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="G11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="11" t="n">
+      <c r="G11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1730,25 +1760,25 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="13" t="n">
         <v>0.275</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="13" t="n">
         <v>0.325</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="13" t="n">
         <v>0.175</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="13" t="n">
         <v>0.15</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="13" t="n">
         <v>0.05</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="H12" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1758,25 +1788,25 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="13" t="n">
         <v>0.2608695652173913</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="13" t="n">
         <v>0.2173913043478261</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="13" t="n">
         <v>0.3043478260869565</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="13" t="n">
         <v>0.1304347826086956</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F13" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="G13" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="H13" s="11" t="n">
+      <c r="H13" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1786,32 +1816,32 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="14" t="n">
         <v>0.303030303030303</v>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="14" t="n">
         <v>0.2929292929292929</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="14" t="n">
         <v>0.2222222222222222</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="14" t="n">
         <v>0.1212121212121212</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="14" t="n">
         <v>0.04040404040404041</v>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="G14" s="14" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="H14" s="11" t="n">
+      <c r="H14" s="15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15"/>
     <row r="16"/>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>suburb_cnt</t>
         </is>
@@ -1940,70 +1970,70 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="8" t="n">
+      <c r="B19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="8" t="n">
+      <c r="E19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="W19" s="9" t="n">
+      <c r="W19" s="11" t="n">
         <v>36</v>
       </c>
     </row>
@@ -2013,70 +2043,70 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="8" t="n">
+      <c r="B20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="W20" s="9" t="n">
+      <c r="W20" s="11" t="n">
         <v>40</v>
       </c>
     </row>
@@ -2086,70 +2116,70 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="8" t="n">
+      <c r="B21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="8" t="n">
+      <c r="G21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="W21" s="9" t="n">
+      <c r="W21" s="11" t="n">
         <v>23</v>
       </c>
     </row>
@@ -2159,77 +2189,77 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="G22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" s="9" t="n">
+      <c r="G22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="11" t="n">
         <v>74</v>
       </c>
-      <c r="W22" s="9" t="n">
+      <c r="W22" s="12" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="23"/>
     <row r="24"/>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>suburb_pct</t>
         </is>
@@ -2358,70 +2388,70 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n">
+      <c r="B27" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C27" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="D27" s="10" t="n">
+      <c r="D27" s="13" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="E27" s="10" t="n">
+      <c r="E27" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="F27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="10" t="n">
+      <c r="F27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="K27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="10" t="n">
+      <c r="K27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="M27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="10" t="n">
+      <c r="M27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="P27" s="10" t="n">
+      <c r="P27" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="Q27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" s="10" t="n">
+      <c r="Q27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="U27" s="10" t="n">
+      <c r="U27" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="V27" s="10" t="n">
+      <c r="V27" s="13" t="n">
         <v>0.6944444444444444</v>
       </c>
-      <c r="W27" s="11" t="n">
+      <c r="W27" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2431,70 +2461,70 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="10" t="n">
+      <c r="B28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="D28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="10" t="n">
+      <c r="D28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="F28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="10" t="n">
+      <c r="F28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="H28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="10" t="n">
+      <c r="H28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="J28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="10" t="n">
+      <c r="J28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="L28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="10" t="n">
+      <c r="L28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="N28" s="10" t="n">
+      <c r="N28" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="O28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="10" t="n">
+      <c r="O28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="R28" s="10" t="n">
+      <c r="R28" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="S28" s="10" t="n">
+      <c r="S28" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="T28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="10" t="n">
+      <c r="T28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="13" t="n">
         <v>0.75</v>
       </c>
-      <c r="W28" s="11" t="n">
+      <c r="W28" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2504,70 +2534,70 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n">
+      <c r="B29" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="C29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="10" t="n">
+      <c r="C29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="13" t="n">
         <v>0.08695652173913043</v>
       </c>
-      <c r="G29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="10" t="n">
+      <c r="G29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="I29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="10" t="n">
+      <c r="I29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="13" t="n">
         <v>0.8260869565217391</v>
       </c>
-      <c r="W29" s="11" t="n">
+      <c r="W29" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2577,70 +2607,70 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B30" s="14" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="C30" s="11" t="n">
+      <c r="C30" s="14" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="D30" s="14" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="E30" s="11" t="n">
+      <c r="E30" s="14" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="F30" s="11" t="n">
+      <c r="F30" s="14" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="G30" s="11" t="n">
+      <c r="G30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="H30" s="11" t="n">
+      <c r="H30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="I30" s="11" t="n">
+      <c r="I30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="J30" s="11" t="n">
+      <c r="J30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="K30" s="11" t="n">
+      <c r="K30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="L30" s="11" t="n">
+      <c r="L30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="M30" s="11" t="n">
+      <c r="M30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="N30" s="11" t="n">
+      <c r="N30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="O30" s="11" t="n">
+      <c r="O30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="P30" s="11" t="n">
+      <c r="P30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="Q30" s="11" t="n">
+      <c r="Q30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="R30" s="11" t="n">
+      <c r="R30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="S30" s="11" t="n">
+      <c r="S30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="T30" s="11" t="n">
+      <c r="T30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="U30" s="11" t="n">
+      <c r="U30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="V30" s="11" t="n">
+      <c r="V30" s="14" t="n">
         <v>0.7474747474747475</v>
       </c>
-      <c r="W30" s="11" t="n">
+      <c r="W30" s="15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2665,7 +2695,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>family_type_cnt</t>
         </is>
@@ -2699,13 +2729,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="D3" s="9" t="n">
+      <c r="D3" s="11" t="n">
         <v>36</v>
       </c>
     </row>
@@ -2715,13 +2745,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="11" t="n">
         <v>40</v>
       </c>
     </row>
@@ -2731,13 +2761,13 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="11" t="n">
         <v>23</v>
       </c>
     </row>
@@ -2747,20 +2777,20 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="11" t="n">
         <v>54</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="12" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="7"/>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>family_type_pct</t>
         </is>
@@ -2794,13 +2824,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="13" t="n">
         <v>0.4444444444444444</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="13" t="n">
         <v>0.5555555555555556</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2810,13 +2840,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="13" t="n">
         <v>0.65</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="13" t="n">
         <v>0.35</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2826,13 +2856,13 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="13" t="n">
         <v>0.5217391304347826</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="13" t="n">
         <v>0.4782608695652174</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2842,13 +2872,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="14" t="n">
         <v>0.5454545454545454</v>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="14" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2875,7 +2905,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>attributed_category_cnt</t>
         </is>
@@ -2919,19 +2949,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="F3" s="11" t="n">
         <v>36</v>
       </c>
     </row>
@@ -2941,19 +2971,19 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="8" t="n">
+      <c r="D4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="11" t="n">
         <v>40</v>
       </c>
     </row>
@@ -2963,19 +2993,19 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="E5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="9" t="n">
+      <c r="E5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="11" t="n">
         <v>23</v>
       </c>
     </row>
@@ -2985,26 +3015,26 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="11" t="n">
         <v>42</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="12" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="7"/>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>attributed_category_pct</t>
         </is>
@@ -3048,19 +3078,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="13" t="n">
         <v>0.25</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="13" t="n">
         <v>0.3888888888888889</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="13" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="13" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3070,19 +3100,19 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="13" t="n">
         <v>0.55</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="13" t="n">
         <v>0.3</v>
       </c>
-      <c r="D12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="10" t="n">
+      <c r="D12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="13" t="n">
         <v>0.15</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3092,19 +3122,19 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="13" t="n">
         <v>0.4782608695652174</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="13" t="n">
         <v>0.1739130434782609</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="13" t="n">
         <v>0.3043478260869565</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3114,19 +3144,19 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="14" t="n">
         <v>0.4242424242424243</v>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="14" t="n">
         <v>0.303030303030303</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="14" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="14" t="n">
         <v>0.09090909090909091</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3281,7 +3311,7 @@
       <c r="F6" s="6" t="n">
         <v>22335.0925</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="8" t="n">
         <v>26550.73869565217</v>
       </c>
     </row>
@@ -3415,7 +3445,7 @@
       <c r="F14" s="6" t="n">
         <v>12.75</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="8" t="n">
         <v>10.78260869565217</v>
       </c>
     </row>
@@ -3549,7 +3579,7 @@
       <c r="F22" s="6" t="n">
         <v>2.55416477475</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="8" t="n">
         <v>2.972252261217391</v>
       </c>
     </row>
@@ -3683,7 +3713,7 @@
       <c r="F30" s="6" t="n">
         <v>0.99347816025</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G30" s="8" t="n">
         <v>0.954497519826087</v>
       </c>
     </row>
@@ -3739,18 +3769,18 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B35" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="8" t="n">
+      <c r="B35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="D35" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E35" s="8" t="n"/>
-      <c r="F35" s="8" t="n"/>
-      <c r="G35" s="9" t="n">
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3760,20 +3790,20 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B36" s="8" t="n"/>
-      <c r="C36" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="9" t="n">
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3783,16 +3813,16 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B37" s="8" t="n"/>
-      <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="9" t="n">
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3802,22 +3832,22 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B38" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="9" t="n">
+      <c r="B38" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E38" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="9" t="n">
+      <c r="E38" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3861,7 +3891,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>bank_txn_industry_primary_industry_cnt</t>
         </is>
@@ -3945,43 +3975,43 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" s="9" t="n">
+      <c r="D3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="11" t="n">
         <v>36</v>
       </c>
     </row>
@@ -3991,43 +4021,43 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="8" t="n">
+      <c r="E4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="9" t="n">
+      <c r="G4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="11" t="n">
         <v>40</v>
       </c>
     </row>
@@ -4037,43 +4067,43 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="9" t="n">
+      <c r="D5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="11" t="n">
         <v>23</v>
       </c>
     </row>
@@ -4083,50 +4113,50 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="11" t="n">
         <v>76</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" s="9" t="n">
+      <c r="G6" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="12" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="7"/>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>bank_txn_industry_primary_industry_pct</t>
         </is>
@@ -4210,43 +4240,43 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="13" t="n">
         <v>0.75</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="13" t="n">
         <v>0.1388888888888889</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="E11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="10" t="n">
+      <c r="E11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="K11" s="10" t="n">
+      <c r="K11" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="L11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="10" t="n">
+      <c r="L11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="N11" s="11" t="n">
+      <c r="N11" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4256,43 +4286,43 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="13" t="n">
         <v>0.775</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="13" t="n">
         <v>0.05</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="13" t="n">
         <v>0.05</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="13" t="n">
         <v>0.05</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="H12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="10" t="n">
+      <c r="H12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="M12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="11" t="n">
+      <c r="M12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4302,43 +4332,43 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="13" t="n">
         <v>0.7826086956521739</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="13" t="n">
         <v>0.08695652173913043</v>
       </c>
-      <c r="D13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="10" t="n">
+      <c r="D13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="F13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="10" t="n">
+      <c r="F13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="I13" s="10" t="n">
+      <c r="I13" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="J13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="11" t="n">
+      <c r="J13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4348,50 +4378,50 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="14" t="n">
         <v>0.7676767676767676</v>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="14" t="n">
         <v>0.09090909090909091</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="14" t="n">
         <v>0.0303030303030303</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="14" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="14" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="G14" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="H14" s="11" t="n">
+      <c r="H14" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="I14" s="11" t="n">
+      <c r="I14" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="J14" s="11" t="n">
+      <c r="J14" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="K14" s="11" t="n">
+      <c r="K14" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="L14" s="11" t="n">
+      <c r="L14" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="M14" s="11" t="n">
+      <c r="M14" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="N14" s="11" t="n">
+      <c r="N14" s="15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15"/>
     <row r="16"/>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>bank_txn_industry_primary_employer_cnt</t>
         </is>
@@ -4520,70 +4550,70 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B19" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="C19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="8" t="n">
+      <c r="C19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="W19" s="9" t="n">
+      <c r="W19" s="11" t="n">
         <v>36</v>
       </c>
     </row>
@@ -4593,70 +4623,70 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B20" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="C20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="9" t="n">
+      <c r="C20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="11" t="n">
         <v>40</v>
       </c>
     </row>
@@ -4666,70 +4696,70 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n">
+      <c r="B21" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="C21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="8" t="n">
+      <c r="C21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="W21" s="9" t="n">
+      <c r="W21" s="11" t="n">
         <v>23</v>
       </c>
     </row>
@@ -4739,77 +4769,77 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="11" t="n">
         <v>76</v>
       </c>
-      <c r="C22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" s="9" t="n">
+      <c r="C22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="W22" s="9" t="n">
+      <c r="W22" s="12" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="23"/>
     <row r="24"/>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>bank_txn_industry_primary_employer_pct</t>
         </is>
@@ -4938,70 +4968,70 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n">
+      <c r="B27" s="13" t="n">
         <v>0.75</v>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C27" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="D27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="10" t="n">
+      <c r="D27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="K27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="10" t="n">
+      <c r="K27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="M27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="10" t="n">
+      <c r="M27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="O27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="10" t="n">
+      <c r="O27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="R27" s="10" t="n">
+      <c r="R27" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="S27" s="10" t="n">
+      <c r="S27" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="T27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="10" t="n">
+      <c r="T27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="13" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="W27" s="11" t="n">
+      <c r="W27" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5011,70 +5041,70 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n">
+      <c r="B28" s="13" t="n">
         <v>0.775</v>
       </c>
-      <c r="C28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="10" t="n">
+      <c r="C28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="F28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="10" t="n">
+      <c r="F28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="H28" s="10" t="n">
+      <c r="H28" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="I28" s="10" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="J28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="10" t="n">
+      <c r="J28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="L28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="10" t="n">
+      <c r="L28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="N28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="10" t="n">
+      <c r="N28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="P28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" s="10" t="n">
+      <c r="P28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="U28" s="10" t="n">
+      <c r="U28" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="V28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" s="11" t="n">
+      <c r="V28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5084,70 +5114,70 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n">
+      <c r="B29" s="13" t="n">
         <v>0.7826086956521739</v>
       </c>
-      <c r="C29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="10" t="n">
+      <c r="C29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="E29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="10" t="n">
+      <c r="E29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="G29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="10" t="n">
+      <c r="G29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="Q29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="10" t="n">
+      <c r="Q29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="13" t="n">
         <v>0.08695652173913043</v>
       </c>
-      <c r="W29" s="11" t="n">
+      <c r="W29" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5157,70 +5187,70 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B30" s="14" t="n">
         <v>0.7676767676767676</v>
       </c>
-      <c r="C30" s="11" t="n">
+      <c r="C30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="D30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="E30" s="11" t="n">
+      <c r="E30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="F30" s="11" t="n">
+      <c r="F30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="G30" s="11" t="n">
+      <c r="G30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="H30" s="11" t="n">
+      <c r="H30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="I30" s="11" t="n">
+      <c r="I30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="J30" s="11" t="n">
+      <c r="J30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="K30" s="11" t="n">
+      <c r="K30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="L30" s="11" t="n">
+      <c r="L30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="M30" s="11" t="n">
+      <c r="M30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="N30" s="11" t="n">
+      <c r="N30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="O30" s="11" t="n">
+      <c r="O30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="P30" s="11" t="n">
+      <c r="P30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="Q30" s="11" t="n">
+      <c r="Q30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="R30" s="11" t="n">
+      <c r="R30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="S30" s="11" t="n">
+      <c r="S30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="T30" s="11" t="n">
+      <c r="T30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="U30" s="11" t="n">
+      <c r="U30" s="14" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="V30" s="11" t="n">
+      <c r="V30" s="14" t="n">
         <v>0.04040404040404041</v>
       </c>
-      <c r="W30" s="11" t="n">
+      <c r="W30" s="15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5309,7 +5339,7 @@
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="C2" s="10" t="n">
         <v>17</v>
       </c>
       <c r="D2" s="5" t="n">
@@ -5330,7 +5360,7 @@
       <c r="I2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="8" t="n">
+      <c r="J2" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5341,7 +5371,7 @@
       <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="10" t="n">
         <v>14</v>
       </c>
       <c r="D3" s="5" t="n">
@@ -5362,7 +5392,7 @@
       <c r="I3" s="5" t="n">
         <v>0.809511489</v>
       </c>
-      <c r="J3" s="8" t="n">
+      <c r="J3" s="10" t="n">
         <v>1.666666666666667</v>
       </c>
     </row>
@@ -5373,7 +5403,7 @@
       <c r="B4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="10" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="5" t="n">
@@ -5394,7 +5424,7 @@
       <c r="I4" s="5" t="n">
         <v>0.618503498</v>
       </c>
-      <c r="J4" s="8" t="n">
+      <c r="J4" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5405,7 +5435,7 @@
       <c r="B5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="5" t="n">
@@ -5418,7 +5448,7 @@
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
-      <c r="J5" s="8" t="n"/>
+      <c r="J5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -5427,7 +5457,7 @@
       <c r="B6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="5" t="n">
@@ -5440,7 +5470,7 @@
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
-      <c r="J6" s="8" t="n"/>
+      <c r="J6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -5449,7 +5479,7 @@
       <c r="B7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="10" t="n">
         <v>4</v>
       </c>
       <c r="D7" s="5" t="n">
@@ -5462,7 +5492,7 @@
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
-      <c r="J7" s="8" t="n"/>
+      <c r="J7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -5471,7 +5501,7 @@
       <c r="B8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="10" t="n">
         <v>11</v>
       </c>
       <c r="D8" s="5" t="n">
@@ -5492,7 +5522,7 @@
       <c r="I8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="8" t="n">
+      <c r="J8" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5503,7 +5533,7 @@
       <c r="B9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="10" t="n">
         <v>7</v>
       </c>
       <c r="D9" s="5" t="n">
@@ -5524,7 +5554,7 @@
       <c r="I9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="8" t="n">
+      <c r="J9" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5535,7 +5565,7 @@
       <c r="B10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C10" s="10" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="5" t="n">
@@ -5556,7 +5586,7 @@
       <c r="I10" s="5" t="n">
         <v>0.9864984700000001</v>
       </c>
-      <c r="J10" s="8" t="n">
+      <c r="J10" s="10" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -5567,7 +5597,7 @@
       <c r="B11" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="10" t="n">
         <v>6</v>
       </c>
       <c r="D11" s="5" t="n">
@@ -5588,7 +5618,7 @@
       <c r="I11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="8" t="n">
+      <c r="J11" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5599,7 +5629,7 @@
       <c r="B12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="10" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="5" t="n"/>
@@ -5608,7 +5638,7 @@
       <c r="G12" s="5" t="n"/>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="n"/>
-      <c r="J12" s="8" t="n"/>
+      <c r="J12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -5617,7 +5647,7 @@
       <c r="B13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="5" t="n">
@@ -5630,7 +5660,7 @@
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="n"/>
-      <c r="J13" s="8" t="n"/>
+      <c r="J13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -5639,7 +5669,7 @@
       <c r="B14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C14" s="10" t="n">
         <v>3</v>
       </c>
       <c r="D14" s="5" t="n">
@@ -5652,7 +5682,7 @@
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="n"/>
-      <c r="J14" s="8" t="n"/>
+      <c r="J14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -5661,7 +5691,7 @@
       <c r="B15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="10" t="n">
         <v>8</v>
       </c>
       <c r="D15" s="5" t="n">
@@ -5682,7 +5712,7 @@
       <c r="I15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="8" t="n">
+      <c r="J15" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5693,7 +5723,7 @@
       <c r="B16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C16" s="10" t="n">
         <v>11</v>
       </c>
       <c r="D16" s="5" t="n">
@@ -5714,7 +5744,7 @@
       <c r="I16" s="5" t="n">
         <v>0.9913042136666667</v>
       </c>
-      <c r="J16" s="8" t="n">
+      <c r="J16" s="10" t="n">
         <v>1.333333333333333</v>
       </c>
     </row>
@@ -5786,13 +5816,13 @@
           <t>QLD</t>
         </is>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="F2" s="10" t="n">
+      <c r="F2" s="13" t="n">
         <v>0.3611111111111111</v>
       </c>
     </row>
@@ -5810,13 +5840,13 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="F3" s="10" t="n">
+      <c r="F3" s="13" t="n">
         <v>0.3055555555555556</v>
       </c>
     </row>
@@ -5834,13 +5864,13 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="13" t="n">
         <v>0.2222222222222222</v>
       </c>
     </row>
@@ -5858,13 +5888,13 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="13" t="n">
         <v>0.08333333333333333</v>
       </c>
     </row>
@@ -5882,13 +5912,13 @@
           <t>SA</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="10" t="n">
+      <c r="E6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -5906,13 +5936,13 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="10" t="n">
+      <c r="E7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5930,13 +5960,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5954,13 +5984,13 @@
           <t>QLD</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="13" t="n">
         <v>0.275</v>
       </c>
     </row>
@@ -5978,13 +6008,13 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="13" t="n">
         <v>0.325</v>
       </c>
     </row>
@@ -6002,13 +6032,13 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="13" t="n">
         <v>0.175</v>
       </c>
     </row>
@@ -6026,13 +6056,13 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="13" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -6050,13 +6080,13 @@
           <t>SA</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F13" s="13" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -6074,13 +6104,13 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="10" t="n">
+      <c r="E14" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -6098,13 +6128,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E15" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="F15" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6122,13 +6152,13 @@
           <t>QLD</t>
         </is>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="E16" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="F16" s="13" t="n">
         <v>0.2608695652173913</v>
       </c>
     </row>
@@ -6146,13 +6176,13 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="E17" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="13" t="n">
         <v>0.2173913043478261</v>
       </c>
     </row>
@@ -6170,13 +6200,13 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D18" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="E18" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="13" t="n">
         <v>0.3043478260869565</v>
       </c>
     </row>
@@ -6194,13 +6224,13 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E19" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="13" t="n">
         <v>0.1304347826086956</v>
       </c>
     </row>
@@ -6218,13 +6248,13 @@
           <t>SA</t>
         </is>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="10" t="n">
+      <c r="E20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
     </row>
@@ -6242,13 +6272,13 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="10" t="n">
+      <c r="E21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
     </row>
@@ -6266,13 +6296,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E22" s="8" t="n">
+      <c r="E22" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="F22" s="10" t="n">
+      <c r="F22" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6292,13 +6322,13 @@
           <t>QLD</t>
         </is>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="E23" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="F23" s="10" t="n">
+      <c r="F23" s="13" t="n">
         <v>0.303030303030303</v>
       </c>
     </row>
@@ -6318,13 +6348,13 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D24" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="13" t="n">
         <v>0.2929292929292929</v>
       </c>
     </row>
@@ -6344,13 +6374,13 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D25" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="E25" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="F25" s="10" t="n">
+      <c r="F25" s="13" t="n">
         <v>0.2222222222222222</v>
       </c>
     </row>
@@ -6370,13 +6400,13 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="D26" s="8" t="n">
+      <c r="D26" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="E26" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="F26" s="10" t="n">
+      <c r="F26" s="13" t="n">
         <v>0.1212121212121212</v>
       </c>
     </row>
@@ -6396,13 +6426,13 @@
           <t>SA</t>
         </is>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="D27" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="E27" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" s="13" t="n">
         <v>0.04040404040404041</v>
       </c>
     </row>
@@ -6422,13 +6452,13 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="D28" s="8" t="n">
+      <c r="D28" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E28" s="8" t="n">
+      <c r="E28" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F28" s="10" t="n">
+      <c r="F28" s="13" t="n">
         <v>0.0202020202020202</v>
       </c>
     </row>
@@ -6448,13 +6478,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="D29" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="E29" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="F29" s="10" t="n">
+      <c r="F29" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6472,13 +6502,13 @@
           <t>Kallangur</t>
         </is>
       </c>
-      <c r="D30" s="8" t="n">
+      <c r="D30" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E30" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="10" t="n">
+      <c r="E30" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -6496,13 +6526,13 @@
           <t>Moree</t>
         </is>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="D31" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E31" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="10" t="n">
+      <c r="E31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -6520,13 +6550,13 @@
           <t>Ningi</t>
         </is>
       </c>
-      <c r="D32" s="8" t="n">
+      <c r="D32" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E32" s="8" t="n">
+      <c r="E32" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F32" s="10" t="n">
+      <c r="F32" s="13" t="n">
         <v>0.05555555555555555</v>
       </c>
     </row>
@@ -6544,13 +6574,13 @@
           <t>Smithfield</t>
         </is>
       </c>
-      <c r="D33" s="8" t="n">
+      <c r="D33" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E33" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="10" t="n">
+      <c r="E33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -6568,13 +6598,13 @@
           <t>Tarneit</t>
         </is>
       </c>
-      <c r="D34" s="8" t="n">
+      <c r="D34" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="10" t="n">
+      <c r="E34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6592,13 +6622,13 @@
           <t>Ashmore</t>
         </is>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="D35" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="10" t="n">
+      <c r="E35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6616,13 +6646,13 @@
           <t>Auburn</t>
         </is>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="D36" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E36" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="10" t="n">
+      <c r="E36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6640,13 +6670,13 @@
           <t>Balga</t>
         </is>
       </c>
-      <c r="D37" s="8" t="n">
+      <c r="D37" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E37" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="10" t="n">
+      <c r="E37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6664,13 +6694,13 @@
           <t>Beaumont Hills</t>
         </is>
       </c>
-      <c r="D38" s="8" t="n">
+      <c r="D38" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E38" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="10" t="n">
+      <c r="E38" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -6688,13 +6718,13 @@
           <t>Black Head</t>
         </is>
       </c>
-      <c r="D39" s="8" t="n">
+      <c r="D39" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E39" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="10" t="n">
+      <c r="E39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6712,13 +6742,13 @@
           <t>Blackalls Park</t>
         </is>
       </c>
-      <c r="D40" s="8" t="n">
+      <c r="D40" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E40" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="10" t="n">
+      <c r="E40" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -6736,13 +6766,13 @@
           <t>Blackwater</t>
         </is>
       </c>
-      <c r="D41" s="8" t="n">
+      <c r="D41" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E41" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="10" t="n">
+      <c r="E41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6760,13 +6790,13 @@
           <t>Boronia Heights</t>
         </is>
       </c>
-      <c r="D42" s="8" t="n">
+      <c r="D42" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E42" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="10" t="n">
+      <c r="E42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6784,13 +6814,13 @@
           <t>Boyup Brook</t>
         </is>
       </c>
-      <c r="D43" s="8" t="n">
+      <c r="D43" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E43" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="10" t="n">
+      <c r="E43" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -6808,13 +6838,13 @@
           <t>Brisbane City</t>
         </is>
       </c>
-      <c r="D44" s="8" t="n">
+      <c r="D44" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E44" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="10" t="n">
+      <c r="E44" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -6832,13 +6862,13 @@
           <t>Broken Hill</t>
         </is>
       </c>
-      <c r="D45" s="8" t="n">
+      <c r="D45" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E45" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="10" t="n">
+      <c r="E45" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6856,13 +6886,13 @@
           <t>Bushland Beach</t>
         </is>
       </c>
-      <c r="D46" s="8" t="n">
+      <c r="D46" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E46" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="10" t="n">
+      <c r="E46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6880,13 +6910,13 @@
           <t>Cambridge Park</t>
         </is>
       </c>
-      <c r="D47" s="8" t="n">
+      <c r="D47" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E47" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="10" t="n">
+      <c r="E47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6904,13 +6934,13 @@
           <t>Chermside</t>
         </is>
       </c>
-      <c r="D48" s="8" t="n">
+      <c r="D48" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E48" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="10" t="n">
+      <c r="E48" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -6928,13 +6958,13 @@
           <t>Clinton</t>
         </is>
       </c>
-      <c r="D49" s="8" t="n">
+      <c r="D49" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E49" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="10" t="n">
+      <c r="E49" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -6952,13 +6982,13 @@
           <t>Others</t>
         </is>
       </c>
-      <c r="D50" s="8" t="n">
+      <c r="D50" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E50" s="8" t="n">
+      <c r="E50" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="F50" s="10" t="n">
+      <c r="F50" s="13" t="n">
         <v>0.6944444444444444</v>
       </c>
     </row>
@@ -6976,13 +7006,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D51" s="8" t="n">
+      <c r="D51" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E51" s="8" t="n">
+      <c r="E51" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="F51" s="10" t="n">
+      <c r="F51" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7000,13 +7030,13 @@
           <t>Kallangur</t>
         </is>
       </c>
-      <c r="D52" s="8" t="n">
+      <c r="D52" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E52" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="10" t="n">
+      <c r="E52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7024,13 +7054,13 @@
           <t>Moree</t>
         </is>
       </c>
-      <c r="D53" s="8" t="n">
+      <c r="D53" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E53" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="10" t="n">
+      <c r="E53" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -7048,13 +7078,13 @@
           <t>Ningi</t>
         </is>
       </c>
-      <c r="D54" s="8" t="n">
+      <c r="D54" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E54" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="10" t="n">
+      <c r="E54" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7072,13 +7102,13 @@
           <t>Smithfield</t>
         </is>
       </c>
-      <c r="D55" s="8" t="n">
+      <c r="D55" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E55" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" s="10" t="n">
+      <c r="E55" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -7096,13 +7126,13 @@
           <t>Tarneit</t>
         </is>
       </c>
-      <c r="D56" s="8" t="n">
+      <c r="D56" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E56" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="10" t="n">
+      <c r="E56" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7120,13 +7150,13 @@
           <t>Ashmore</t>
         </is>
       </c>
-      <c r="D57" s="8" t="n">
+      <c r="D57" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E57" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" s="10" t="n">
+      <c r="E57" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -7144,13 +7174,13 @@
           <t>Auburn</t>
         </is>
       </c>
-      <c r="D58" s="8" t="n">
+      <c r="D58" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E58" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="10" t="n">
+      <c r="E58" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7168,13 +7198,13 @@
           <t>Balga</t>
         </is>
       </c>
-      <c r="D59" s="8" t="n">
+      <c r="D59" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E59" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" s="10" t="n">
+      <c r="E59" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -7192,13 +7222,13 @@
           <t>Beaumont Hills</t>
         </is>
       </c>
-      <c r="D60" s="8" t="n">
+      <c r="D60" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E60" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="10" t="n">
+      <c r="E60" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7216,13 +7246,13 @@
           <t>Black Head</t>
         </is>
       </c>
-      <c r="D61" s="8" t="n">
+      <c r="D61" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E61" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" s="10" t="n">
+      <c r="E61" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -7240,13 +7270,13 @@
           <t>Blackalls Park</t>
         </is>
       </c>
-      <c r="D62" s="8" t="n">
+      <c r="D62" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E62" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="10" t="n">
+      <c r="E62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7264,13 +7294,13 @@
           <t>Blackwater</t>
         </is>
       </c>
-      <c r="D63" s="8" t="n">
+      <c r="D63" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E63" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="10" t="n">
+      <c r="E63" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -7288,13 +7318,13 @@
           <t>Boronia Heights</t>
         </is>
       </c>
-      <c r="D64" s="8" t="n">
+      <c r="D64" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E64" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" s="10" t="n">
+      <c r="E64" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -7312,13 +7342,13 @@
           <t>Boyup Brook</t>
         </is>
       </c>
-      <c r="D65" s="8" t="n">
+      <c r="D65" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E65" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="10" t="n">
+      <c r="E65" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7336,13 +7366,13 @@
           <t>Brisbane City</t>
         </is>
       </c>
-      <c r="D66" s="8" t="n">
+      <c r="D66" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E66" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="10" t="n">
+      <c r="E66" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7360,13 +7390,13 @@
           <t>Broken Hill</t>
         </is>
       </c>
-      <c r="D67" s="8" t="n">
+      <c r="D67" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E67" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="10" t="n">
+      <c r="E67" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -7384,13 +7414,13 @@
           <t>Bushland Beach</t>
         </is>
       </c>
-      <c r="D68" s="8" t="n">
+      <c r="D68" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E68" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F68" s="10" t="n">
+      <c r="E68" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -7408,13 +7438,13 @@
           <t>Cambridge Park</t>
         </is>
       </c>
-      <c r="D69" s="8" t="n">
+      <c r="D69" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E69" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F69" s="10" t="n">
+      <c r="E69" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -7432,13 +7462,13 @@
           <t>Chermside</t>
         </is>
       </c>
-      <c r="D70" s="8" t="n">
+      <c r="D70" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E70" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="10" t="n">
+      <c r="E70" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7456,13 +7486,13 @@
           <t>Clinton</t>
         </is>
       </c>
-      <c r="D71" s="8" t="n">
+      <c r="D71" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E71" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="10" t="n">
+      <c r="E71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7480,13 +7510,13 @@
           <t>Others</t>
         </is>
       </c>
-      <c r="D72" s="8" t="n">
+      <c r="D72" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E72" s="8" t="n">
+      <c r="E72" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="F72" s="10" t="n">
+      <c r="F72" s="13" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -7504,13 +7534,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D73" s="8" t="n">
+      <c r="D73" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E73" s="8" t="n">
+      <c r="E73" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="F73" s="10" t="n">
+      <c r="F73" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7528,13 +7558,13 @@
           <t>Kallangur</t>
         </is>
       </c>
-      <c r="D74" s="8" t="n">
+      <c r="D74" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E74" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" s="10" t="n">
+      <c r="E74" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
     </row>
@@ -7552,13 +7582,13 @@
           <t>Moree</t>
         </is>
       </c>
-      <c r="D75" s="8" t="n">
+      <c r="D75" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E75" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="10" t="n">
+      <c r="E75" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7576,13 +7606,13 @@
           <t>Ningi</t>
         </is>
       </c>
-      <c r="D76" s="8" t="n">
+      <c r="D76" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E76" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" s="10" t="n">
+      <c r="E76" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7600,13 +7630,13 @@
           <t>Smithfield</t>
         </is>
       </c>
-      <c r="D77" s="8" t="n">
+      <c r="D77" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E77" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" s="10" t="n">
+      <c r="E77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7624,13 +7654,13 @@
           <t>Tarneit</t>
         </is>
       </c>
-      <c r="D78" s="8" t="n">
+      <c r="D78" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E78" s="8" t="n">
+      <c r="E78" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F78" s="10" t="n">
+      <c r="F78" s="13" t="n">
         <v>0.08695652173913043</v>
       </c>
     </row>
@@ -7648,13 +7678,13 @@
           <t>Ashmore</t>
         </is>
       </c>
-      <c r="D79" s="8" t="n">
+      <c r="D79" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E79" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="10" t="n">
+      <c r="E79" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7672,13 +7702,13 @@
           <t>Auburn</t>
         </is>
       </c>
-      <c r="D80" s="8" t="n">
+      <c r="D80" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E80" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" s="10" t="n">
+      <c r="E80" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
     </row>
@@ -7696,13 +7726,13 @@
           <t>Balga</t>
         </is>
       </c>
-      <c r="D81" s="8" t="n">
+      <c r="D81" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E81" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="10" t="n">
+      <c r="E81" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7720,13 +7750,13 @@
           <t>Beaumont Hills</t>
         </is>
       </c>
-      <c r="D82" s="8" t="n">
+      <c r="D82" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E82" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="10" t="n">
+      <c r="E82" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7744,13 +7774,13 @@
           <t>Black Head</t>
         </is>
       </c>
-      <c r="D83" s="8" t="n">
+      <c r="D83" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E83" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="10" t="n">
+      <c r="E83" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7768,13 +7798,13 @@
           <t>Blackalls Park</t>
         </is>
       </c>
-      <c r="D84" s="8" t="n">
+      <c r="D84" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E84" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="10" t="n">
+      <c r="E84" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7792,13 +7822,13 @@
           <t>Blackwater</t>
         </is>
       </c>
-      <c r="D85" s="8" t="n">
+      <c r="D85" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E85" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="10" t="n">
+      <c r="E85" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7816,13 +7846,13 @@
           <t>Boronia Heights</t>
         </is>
       </c>
-      <c r="D86" s="8" t="n">
+      <c r="D86" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E86" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="10" t="n">
+      <c r="E86" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7840,13 +7870,13 @@
           <t>Boyup Brook</t>
         </is>
       </c>
-      <c r="D87" s="8" t="n">
+      <c r="D87" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E87" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="10" t="n">
+      <c r="E87" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7864,13 +7894,13 @@
           <t>Brisbane City</t>
         </is>
       </c>
-      <c r="D88" s="8" t="n">
+      <c r="D88" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E88" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="10" t="n">
+      <c r="E88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7888,13 +7918,13 @@
           <t>Broken Hill</t>
         </is>
       </c>
-      <c r="D89" s="8" t="n">
+      <c r="D89" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E89" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="10" t="n">
+      <c r="E89" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7912,13 +7942,13 @@
           <t>Bushland Beach</t>
         </is>
       </c>
-      <c r="D90" s="8" t="n">
+      <c r="D90" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E90" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" s="10" t="n">
+      <c r="E90" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7936,13 +7966,13 @@
           <t>Cambridge Park</t>
         </is>
       </c>
-      <c r="D91" s="8" t="n">
+      <c r="D91" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E91" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="10" t="n">
+      <c r="E91" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7960,13 +7990,13 @@
           <t>Chermside</t>
         </is>
       </c>
-      <c r="D92" s="8" t="n">
+      <c r="D92" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E92" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" s="10" t="n">
+      <c r="E92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7984,13 +8014,13 @@
           <t>Clinton</t>
         </is>
       </c>
-      <c r="D93" s="8" t="n">
+      <c r="D93" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E93" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" s="10" t="n">
+      <c r="E93" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8008,13 +8038,13 @@
           <t>Others</t>
         </is>
       </c>
-      <c r="D94" s="8" t="n">
+      <c r="D94" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E94" s="8" t="n">
+      <c r="E94" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="F94" s="10" t="n">
+      <c r="F94" s="13" t="n">
         <v>0.8260869565217391</v>
       </c>
     </row>
@@ -8032,13 +8062,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D95" s="8" t="n">
+      <c r="D95" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E95" s="8" t="n">
+      <c r="E95" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="F95" s="10" t="n">
+      <c r="F95" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8058,13 +8088,13 @@
           <t>Kallangur</t>
         </is>
       </c>
-      <c r="D96" s="8" t="n">
+      <c r="D96" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E96" s="8" t="n">
+      <c r="E96" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F96" s="10" t="n">
+      <c r="F96" s="13" t="n">
         <v>0.0202020202020202</v>
       </c>
     </row>
@@ -8084,13 +8114,13 @@
           <t>Moree</t>
         </is>
       </c>
-      <c r="D97" s="8" t="n">
+      <c r="D97" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E97" s="8" t="n">
+      <c r="E97" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F97" s="10" t="n">
+      <c r="F97" s="13" t="n">
         <v>0.0202020202020202</v>
       </c>
     </row>
@@ -8110,13 +8140,13 @@
           <t>Ningi</t>
         </is>
       </c>
-      <c r="D98" s="8" t="n">
+      <c r="D98" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E98" s="8" t="n">
+      <c r="E98" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F98" s="10" t="n">
+      <c r="F98" s="13" t="n">
         <v>0.0202020202020202</v>
       </c>
     </row>
@@ -8136,13 +8166,13 @@
           <t>Smithfield</t>
         </is>
       </c>
-      <c r="D99" s="8" t="n">
+      <c r="D99" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E99" s="8" t="n">
+      <c r="E99" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F99" s="10" t="n">
+      <c r="F99" s="13" t="n">
         <v>0.0202020202020202</v>
       </c>
     </row>
@@ -8162,13 +8192,13 @@
           <t>Tarneit</t>
         </is>
       </c>
-      <c r="D100" s="8" t="n">
+      <c r="D100" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E100" s="8" t="n">
+      <c r="E100" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F100" s="10" t="n">
+      <c r="F100" s="13" t="n">
         <v>0.0202020202020202</v>
       </c>
     </row>
@@ -8188,13 +8218,13 @@
           <t>Ashmore</t>
         </is>
       </c>
-      <c r="D101" s="8" t="n">
+      <c r="D101" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E101" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F101" s="10" t="n">
+      <c r="E101" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -8214,13 +8244,13 @@
           <t>Auburn</t>
         </is>
       </c>
-      <c r="D102" s="8" t="n">
+      <c r="D102" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E102" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F102" s="10" t="n">
+      <c r="E102" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -8240,13 +8270,13 @@
           <t>Balga</t>
         </is>
       </c>
-      <c r="D103" s="8" t="n">
+      <c r="D103" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E103" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F103" s="10" t="n">
+      <c r="E103" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -8266,13 +8296,13 @@
           <t>Beaumont Hills</t>
         </is>
       </c>
-      <c r="D104" s="8" t="n">
+      <c r="D104" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E104" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F104" s="10" t="n">
+      <c r="E104" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -8292,13 +8322,13 @@
           <t>Black Head</t>
         </is>
       </c>
-      <c r="D105" s="8" t="n">
+      <c r="D105" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E105" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F105" s="10" t="n">
+      <c r="E105" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -8318,13 +8348,13 @@
           <t>Blackalls Park</t>
         </is>
       </c>
-      <c r="D106" s="8" t="n">
+      <c r="D106" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E106" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F106" s="10" t="n">
+      <c r="E106" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -8344,13 +8374,13 @@
           <t>Blackwater</t>
         </is>
       </c>
-      <c r="D107" s="8" t="n">
+      <c r="D107" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E107" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F107" s="10" t="n">
+      <c r="E107" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -8370,13 +8400,13 @@
           <t>Boronia Heights</t>
         </is>
       </c>
-      <c r="D108" s="8" t="n">
+      <c r="D108" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E108" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F108" s="10" t="n">
+      <c r="E108" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -8396,13 +8426,13 @@
           <t>Boyup Brook</t>
         </is>
       </c>
-      <c r="D109" s="8" t="n">
+      <c r="D109" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E109" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F109" s="10" t="n">
+      <c r="E109" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -8422,13 +8452,13 @@
           <t>Brisbane City</t>
         </is>
       </c>
-      <c r="D110" s="8" t="n">
+      <c r="D110" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E110" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F110" s="10" t="n">
+      <c r="E110" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -8448,13 +8478,13 @@
           <t>Broken Hill</t>
         </is>
       </c>
-      <c r="D111" s="8" t="n">
+      <c r="D111" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E111" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F111" s="10" t="n">
+      <c r="E111" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -8474,13 +8504,13 @@
           <t>Bushland Beach</t>
         </is>
       </c>
-      <c r="D112" s="8" t="n">
+      <c r="D112" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E112" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F112" s="10" t="n">
+      <c r="E112" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -8500,13 +8530,13 @@
           <t>Cambridge Park</t>
         </is>
       </c>
-      <c r="D113" s="8" t="n">
+      <c r="D113" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E113" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F113" s="10" t="n">
+      <c r="E113" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -8526,13 +8556,13 @@
           <t>Chermside</t>
         </is>
       </c>
-      <c r="D114" s="8" t="n">
+      <c r="D114" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E114" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F114" s="10" t="n">
+      <c r="E114" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -8552,13 +8582,13 @@
           <t>Clinton</t>
         </is>
       </c>
-      <c r="D115" s="8" t="n">
+      <c r="D115" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E115" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F115" s="10" t="n">
+      <c r="E115" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -8578,13 +8608,13 @@
           <t>Others</t>
         </is>
       </c>
-      <c r="D116" s="8" t="n">
+      <c r="D116" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E116" s="8" t="n">
+      <c r="E116" s="10" t="n">
         <v>74</v>
       </c>
-      <c r="F116" s="10" t="n">
+      <c r="F116" s="13" t="n">
         <v>0.7474747474747475</v>
       </c>
     </row>
@@ -8604,13 +8634,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D117" s="8" t="n">
+      <c r="D117" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E117" s="8" t="n">
+      <c r="E117" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="F117" s="10" t="n">
+      <c r="F117" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8628,13 +8658,13 @@
           <t>single</t>
         </is>
       </c>
-      <c r="D118" s="8" t="n">
+      <c r="D118" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E118" s="8" t="n">
+      <c r="E118" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="F118" s="10" t="n">
+      <c r="F118" s="13" t="n">
         <v>0.4444444444444444</v>
       </c>
     </row>
@@ -8652,13 +8682,13 @@
           <t>couple</t>
         </is>
       </c>
-      <c r="D119" s="8" t="n">
+      <c r="D119" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E119" s="8" t="n">
+      <c r="E119" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="F119" s="10" t="n">
+      <c r="F119" s="13" t="n">
         <v>0.5555555555555556</v>
       </c>
     </row>
@@ -8676,13 +8706,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D120" s="8" t="n">
+      <c r="D120" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E120" s="8" t="n">
+      <c r="E120" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="F120" s="10" t="n">
+      <c r="F120" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8700,13 +8730,13 @@
           <t>single</t>
         </is>
       </c>
-      <c r="D121" s="8" t="n">
+      <c r="D121" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E121" s="8" t="n">
+      <c r="E121" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="F121" s="10" t="n">
+      <c r="F121" s="13" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -8724,13 +8754,13 @@
           <t>couple</t>
         </is>
       </c>
-      <c r="D122" s="8" t="n">
+      <c r="D122" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E122" s="8" t="n">
+      <c r="E122" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="F122" s="10" t="n">
+      <c r="F122" s="13" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -8748,13 +8778,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D123" s="8" t="n">
+      <c r="D123" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E123" s="8" t="n">
+      <c r="E123" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="F123" s="10" t="n">
+      <c r="F123" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8772,13 +8802,13 @@
           <t>single</t>
         </is>
       </c>
-      <c r="D124" s="8" t="n">
+      <c r="D124" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E124" s="8" t="n">
+      <c r="E124" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="F124" s="10" t="n">
+      <c r="F124" s="13" t="n">
         <v>0.5217391304347826</v>
       </c>
     </row>
@@ -8796,13 +8826,13 @@
           <t>couple</t>
         </is>
       </c>
-      <c r="D125" s="8" t="n">
+      <c r="D125" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E125" s="8" t="n">
+      <c r="E125" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="F125" s="10" t="n">
+      <c r="F125" s="13" t="n">
         <v>0.4782608695652174</v>
       </c>
     </row>
@@ -8820,13 +8850,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D126" s="8" t="n">
+      <c r="D126" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E126" s="8" t="n">
+      <c r="E126" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="F126" s="10" t="n">
+      <c r="F126" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8846,13 +8876,13 @@
           <t>single</t>
         </is>
       </c>
-      <c r="D127" s="8" t="n">
+      <c r="D127" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E127" s="8" t="n">
+      <c r="E127" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="F127" s="10" t="n">
+      <c r="F127" s="13" t="n">
         <v>0.5454545454545454</v>
       </c>
     </row>
@@ -8872,13 +8902,13 @@
           <t>couple</t>
         </is>
       </c>
-      <c r="D128" s="8" t="n">
+      <c r="D128" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E128" s="8" t="n">
+      <c r="E128" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="F128" s="10" t="n">
+      <c r="F128" s="13" t="n">
         <v>0.4545454545454545</v>
       </c>
     </row>
@@ -8898,13 +8928,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D129" s="8" t="n">
+      <c r="D129" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E129" s="8" t="n">
+      <c r="E129" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="F129" s="10" t="n">
+      <c r="F129" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8922,13 +8952,13 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="D130" s="8" t="n">
+      <c r="D130" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E130" s="8" t="n">
+      <c r="E130" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="F130" s="10" t="n">
+      <c r="F130" s="13" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -8946,13 +8976,13 @@
           <t>Organic</t>
         </is>
       </c>
-      <c r="D131" s="8" t="n">
+      <c r="D131" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E131" s="8" t="n">
+      <c r="E131" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="F131" s="10" t="n">
+      <c r="F131" s="13" t="n">
         <v>0.3888888888888889</v>
       </c>
     </row>
@@ -8970,13 +9000,13 @@
           <t>Lead Partner</t>
         </is>
       </c>
-      <c r="D132" s="8" t="n">
+      <c r="D132" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E132" s="8" t="n">
+      <c r="E132" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="F132" s="10" t="n">
+      <c r="F132" s="13" t="n">
         <v>0.3055555555555556</v>
       </c>
     </row>
@@ -8994,13 +9024,13 @@
           <t>Owned Channels</t>
         </is>
       </c>
-      <c r="D133" s="8" t="n">
+      <c r="D133" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E133" s="8" t="n">
+      <c r="E133" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F133" s="10" t="n">
+      <c r="F133" s="13" t="n">
         <v>0.05555555555555555</v>
       </c>
     </row>
@@ -9018,13 +9048,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D134" s="8" t="n">
+      <c r="D134" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E134" s="8" t="n">
+      <c r="E134" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="F134" s="10" t="n">
+      <c r="F134" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9042,13 +9072,13 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="D135" s="8" t="n">
+      <c r="D135" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E135" s="8" t="n">
+      <c r="E135" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="F135" s="10" t="n">
+      <c r="F135" s="13" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -9066,13 +9096,13 @@
           <t>Organic</t>
         </is>
       </c>
-      <c r="D136" s="8" t="n">
+      <c r="D136" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E136" s="8" t="n">
+      <c r="E136" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="F136" s="10" t="n">
+      <c r="F136" s="13" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -9090,13 +9120,13 @@
           <t>Lead Partner</t>
         </is>
       </c>
-      <c r="D137" s="8" t="n">
+      <c r="D137" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E137" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F137" s="10" t="n">
+      <c r="E137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9114,13 +9144,13 @@
           <t>Owned Channels</t>
         </is>
       </c>
-      <c r="D138" s="8" t="n">
+      <c r="D138" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E138" s="8" t="n">
+      <c r="E138" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="F138" s="10" t="n">
+      <c r="F138" s="13" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -9138,13 +9168,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D139" s="8" t="n">
+      <c r="D139" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E139" s="8" t="n">
+      <c r="E139" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="F139" s="10" t="n">
+      <c r="F139" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9162,13 +9192,13 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="D140" s="8" t="n">
+      <c r="D140" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E140" s="8" t="n">
+      <c r="E140" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="F140" s="10" t="n">
+      <c r="F140" s="13" t="n">
         <v>0.4782608695652174</v>
       </c>
     </row>
@@ -9186,13 +9216,13 @@
           <t>Organic</t>
         </is>
       </c>
-      <c r="D141" s="8" t="n">
+      <c r="D141" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E141" s="8" t="n">
+      <c r="E141" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="F141" s="10" t="n">
+      <c r="F141" s="13" t="n">
         <v>0.1739130434782609</v>
       </c>
     </row>
@@ -9210,13 +9240,13 @@
           <t>Lead Partner</t>
         </is>
       </c>
-      <c r="D142" s="8" t="n">
+      <c r="D142" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E142" s="8" t="n">
+      <c r="E142" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="F142" s="10" t="n">
+      <c r="F142" s="13" t="n">
         <v>0.3043478260869565</v>
       </c>
     </row>
@@ -9234,13 +9264,13 @@
           <t>Owned Channels</t>
         </is>
       </c>
-      <c r="D143" s="8" t="n">
+      <c r="D143" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E143" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F143" s="10" t="n">
+      <c r="E143" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
     </row>
@@ -9258,13 +9288,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D144" s="8" t="n">
+      <c r="D144" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E144" s="8" t="n">
+      <c r="E144" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="F144" s="10" t="n">
+      <c r="F144" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9284,13 +9314,13 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="D145" s="8" t="n">
+      <c r="D145" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E145" s="8" t="n">
+      <c r="E145" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="F145" s="10" t="n">
+      <c r="F145" s="13" t="n">
         <v>0.4242424242424243</v>
       </c>
     </row>
@@ -9310,13 +9340,13 @@
           <t>Organic</t>
         </is>
       </c>
-      <c r="D146" s="8" t="n">
+      <c r="D146" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E146" s="8" t="n">
+      <c r="E146" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="F146" s="10" t="n">
+      <c r="F146" s="13" t="n">
         <v>0.303030303030303</v>
       </c>
     </row>
@@ -9336,13 +9366,13 @@
           <t>Lead Partner</t>
         </is>
       </c>
-      <c r="D147" s="8" t="n">
+      <c r="D147" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E147" s="8" t="n">
+      <c r="E147" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="F147" s="10" t="n">
+      <c r="F147" s="13" t="n">
         <v>0.1818181818181818</v>
       </c>
     </row>
@@ -9362,13 +9392,13 @@
           <t>Owned Channels</t>
         </is>
       </c>
-      <c r="D148" s="8" t="n">
+      <c r="D148" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E148" s="8" t="n">
+      <c r="E148" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="F148" s="10" t="n">
+      <c r="F148" s="13" t="n">
         <v>0.09090909090909091</v>
       </c>
     </row>
@@ -9388,13 +9418,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D149" s="8" t="n">
+      <c r="D149" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E149" s="8" t="n">
+      <c r="E149" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="F149" s="10" t="n">
+      <c r="F149" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9412,13 +9442,13 @@
           <t>Missing</t>
         </is>
       </c>
-      <c r="D150" s="8" t="n">
+      <c r="D150" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E150" s="8" t="n">
+      <c r="E150" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="F150" s="10" t="n">
+      <c r="F150" s="13" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -9436,13 +9466,13 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D151" s="8" t="n">
+      <c r="D151" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E151" s="8" t="n">
+      <c r="E151" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F151" s="10" t="n">
+      <c r="F151" s="13" t="n">
         <v>0.1388888888888889</v>
       </c>
     </row>
@@ -9460,13 +9490,13 @@
           <t>Retail Trade</t>
         </is>
       </c>
-      <c r="D152" s="8" t="n">
+      <c r="D152" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E152" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F152" s="10" t="n">
+      <c r="E152" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F152" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -9484,13 +9514,13 @@
           <t>Health Care and Social Assistance</t>
         </is>
       </c>
-      <c r="D153" s="8" t="n">
+      <c r="D153" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E153" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F153" s="10" t="n">
+      <c r="E153" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9508,13 +9538,13 @@
           <t>Technical Services/Information Media</t>
         </is>
       </c>
-      <c r="D154" s="8" t="n">
+      <c r="D154" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E154" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F154" s="10" t="n">
+      <c r="E154" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9532,13 +9562,13 @@
           <t>Bank-issued Payroll Distribution</t>
         </is>
       </c>
-      <c r="D155" s="8" t="n">
+      <c r="D155" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E155" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F155" s="10" t="n">
+      <c r="E155" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9556,13 +9586,13 @@
           <t>Cleaning/Security/Property Management</t>
         </is>
       </c>
-      <c r="D156" s="8" t="n">
+      <c r="D156" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E156" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F156" s="10" t="n">
+      <c r="E156" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9580,13 +9610,13 @@
           <t>Construction</t>
         </is>
       </c>
-      <c r="D157" s="8" t="n">
+      <c r="D157" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E157" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F157" s="10" t="n">
+      <c r="E157" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9604,13 +9634,13 @@
           <t>Education and Training</t>
         </is>
       </c>
-      <c r="D158" s="8" t="n">
+      <c r="D158" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E158" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F158" s="10" t="n">
+      <c r="E158" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -9628,13 +9658,13 @@
           <t>Government/Public Administration</t>
         </is>
       </c>
-      <c r="D159" s="8" t="n">
+      <c r="D159" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E159" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F159" s="10" t="n">
+      <c r="E159" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -9652,13 +9682,13 @@
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="D160" s="8" t="n">
+      <c r="D160" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E160" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F160" s="10" t="n">
+      <c r="E160" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9676,13 +9706,13 @@
           <t>Sports/Entertainment/Gambling</t>
         </is>
       </c>
-      <c r="D161" s="8" t="n">
+      <c r="D161" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E161" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F161" s="10" t="n">
+      <c r="E161" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -9700,13 +9730,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D162" s="8" t="n">
+      <c r="D162" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E162" s="8" t="n">
+      <c r="E162" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="F162" s="10" t="n">
+      <c r="F162" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9724,13 +9754,13 @@
           <t>Missing</t>
         </is>
       </c>
-      <c r="D163" s="8" t="n">
+      <c r="D163" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E163" s="8" t="n">
+      <c r="E163" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="F163" s="10" t="n">
+      <c r="F163" s="13" t="n">
         <v>0.775</v>
       </c>
     </row>
@@ -9748,13 +9778,13 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D164" s="8" t="n">
+      <c r="D164" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E164" s="8" t="n">
+      <c r="E164" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F164" s="10" t="n">
+      <c r="F164" s="13" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -9772,13 +9802,13 @@
           <t>Retail Trade</t>
         </is>
       </c>
-      <c r="D165" s="8" t="n">
+      <c r="D165" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E165" s="8" t="n">
+      <c r="E165" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F165" s="10" t="n">
+      <c r="F165" s="13" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -9796,13 +9826,13 @@
           <t>Health Care and Social Assistance</t>
         </is>
       </c>
-      <c r="D166" s="8" t="n">
+      <c r="D166" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E166" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F166" s="10" t="n">
+      <c r="E166" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F166" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -9820,13 +9850,13 @@
           <t>Technical Services/Information Media</t>
         </is>
       </c>
-      <c r="D167" s="8" t="n">
+      <c r="D167" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E167" s="8" t="n">
+      <c r="E167" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F167" s="10" t="n">
+      <c r="F167" s="13" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -9844,13 +9874,13 @@
           <t>Bank-issued Payroll Distribution</t>
         </is>
       </c>
-      <c r="D168" s="8" t="n">
+      <c r="D168" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E168" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F168" s="10" t="n">
+      <c r="E168" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F168" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -9868,13 +9898,13 @@
           <t>Cleaning/Security/Property Management</t>
         </is>
       </c>
-      <c r="D169" s="8" t="n">
+      <c r="D169" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E169" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F169" s="10" t="n">
+      <c r="E169" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9892,13 +9922,13 @@
           <t>Construction</t>
         </is>
       </c>
-      <c r="D170" s="8" t="n">
+      <c r="D170" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E170" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F170" s="10" t="n">
+      <c r="E170" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9916,13 +9946,13 @@
           <t>Education and Training</t>
         </is>
       </c>
-      <c r="D171" s="8" t="n">
+      <c r="D171" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E171" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F171" s="10" t="n">
+      <c r="E171" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9940,13 +9970,13 @@
           <t>Government/Public Administration</t>
         </is>
       </c>
-      <c r="D172" s="8" t="n">
+      <c r="D172" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E172" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F172" s="10" t="n">
+      <c r="E172" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9964,13 +9994,13 @@
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="D173" s="8" t="n">
+      <c r="D173" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E173" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F173" s="10" t="n">
+      <c r="E173" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -9988,13 +10018,13 @@
           <t>Sports/Entertainment/Gambling</t>
         </is>
       </c>
-      <c r="D174" s="8" t="n">
+      <c r="D174" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E174" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F174" s="10" t="n">
+      <c r="E174" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10012,13 +10042,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D175" s="8" t="n">
+      <c r="D175" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E175" s="8" t="n">
+      <c r="E175" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="F175" s="10" t="n">
+      <c r="F175" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10036,13 +10066,13 @@
           <t>Missing</t>
         </is>
       </c>
-      <c r="D176" s="8" t="n">
+      <c r="D176" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E176" s="8" t="n">
+      <c r="E176" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="F176" s="10" t="n">
+      <c r="F176" s="13" t="n">
         <v>0.7826086956521739</v>
       </c>
     </row>
@@ -10060,13 +10090,13 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D177" s="8" t="n">
+      <c r="D177" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E177" s="8" t="n">
+      <c r="E177" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F177" s="10" t="n">
+      <c r="F177" s="13" t="n">
         <v>0.08695652173913043</v>
       </c>
     </row>
@@ -10084,13 +10114,13 @@
           <t>Retail Trade</t>
         </is>
       </c>
-      <c r="D178" s="8" t="n">
+      <c r="D178" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E178" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F178" s="10" t="n">
+      <c r="E178" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10108,13 +10138,13 @@
           <t>Health Care and Social Assistance</t>
         </is>
       </c>
-      <c r="D179" s="8" t="n">
+      <c r="D179" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E179" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F179" s="10" t="n">
+      <c r="E179" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F179" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
     </row>
@@ -10132,13 +10162,13 @@
           <t>Technical Services/Information Media</t>
         </is>
       </c>
-      <c r="D180" s="8" t="n">
+      <c r="D180" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E180" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F180" s="10" t="n">
+      <c r="E180" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10156,13 +10186,13 @@
           <t>Bank-issued Payroll Distribution</t>
         </is>
       </c>
-      <c r="D181" s="8" t="n">
+      <c r="D181" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E181" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F181" s="10" t="n">
+      <c r="E181" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10180,13 +10210,13 @@
           <t>Cleaning/Security/Property Management</t>
         </is>
       </c>
-      <c r="D182" s="8" t="n">
+      <c r="D182" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E182" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F182" s="10" t="n">
+      <c r="E182" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
     </row>
@@ -10204,13 +10234,13 @@
           <t>Construction</t>
         </is>
       </c>
-      <c r="D183" s="8" t="n">
+      <c r="D183" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E183" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F183" s="10" t="n">
+      <c r="E183" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
     </row>
@@ -10228,13 +10258,13 @@
           <t>Education and Training</t>
         </is>
       </c>
-      <c r="D184" s="8" t="n">
+      <c r="D184" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E184" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F184" s="10" t="n">
+      <c r="E184" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10252,13 +10282,13 @@
           <t>Government/Public Administration</t>
         </is>
       </c>
-      <c r="D185" s="8" t="n">
+      <c r="D185" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E185" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F185" s="10" t="n">
+      <c r="E185" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10276,13 +10306,13 @@
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="D186" s="8" t="n">
+      <c r="D186" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E186" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F186" s="10" t="n">
+      <c r="E186" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10300,13 +10330,13 @@
           <t>Sports/Entertainment/Gambling</t>
         </is>
       </c>
-      <c r="D187" s="8" t="n">
+      <c r="D187" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E187" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F187" s="10" t="n">
+      <c r="E187" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10324,13 +10354,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D188" s="8" t="n">
+      <c r="D188" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E188" s="8" t="n">
+      <c r="E188" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="F188" s="10" t="n">
+      <c r="F188" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10350,13 +10380,13 @@
           <t>Missing</t>
         </is>
       </c>
-      <c r="D189" s="8" t="n">
+      <c r="D189" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E189" s="8" t="n">
+      <c r="E189" s="10" t="n">
         <v>76</v>
       </c>
-      <c r="F189" s="10" t="n">
+      <c r="F189" s="13" t="n">
         <v>0.7676767676767676</v>
       </c>
     </row>
@@ -10376,13 +10406,13 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D190" s="8" t="n">
+      <c r="D190" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E190" s="8" t="n">
+      <c r="E190" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="F190" s="10" t="n">
+      <c r="F190" s="13" t="n">
         <v>0.09090909090909091</v>
       </c>
     </row>
@@ -10402,13 +10432,13 @@
           <t>Retail Trade</t>
         </is>
       </c>
-      <c r="D191" s="8" t="n">
+      <c r="D191" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E191" s="8" t="n">
+      <c r="E191" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F191" s="10" t="n">
+      <c r="F191" s="13" t="n">
         <v>0.0303030303030303</v>
       </c>
     </row>
@@ -10428,13 +10458,13 @@
           <t>Health Care and Social Assistance</t>
         </is>
       </c>
-      <c r="D192" s="8" t="n">
+      <c r="D192" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E192" s="8" t="n">
+      <c r="E192" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F192" s="10" t="n">
+      <c r="F192" s="13" t="n">
         <v>0.0202020202020202</v>
       </c>
     </row>
@@ -10454,13 +10484,13 @@
           <t>Technical Services/Information Media</t>
         </is>
       </c>
-      <c r="D193" s="8" t="n">
+      <c r="D193" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E193" s="8" t="n">
+      <c r="E193" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F193" s="10" t="n">
+      <c r="F193" s="13" t="n">
         <v>0.0202020202020202</v>
       </c>
     </row>
@@ -10480,13 +10510,13 @@
           <t>Bank-issued Payroll Distribution</t>
         </is>
       </c>
-      <c r="D194" s="8" t="n">
+      <c r="D194" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E194" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F194" s="10" t="n">
+      <c r="E194" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -10506,13 +10536,13 @@
           <t>Cleaning/Security/Property Management</t>
         </is>
       </c>
-      <c r="D195" s="8" t="n">
+      <c r="D195" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E195" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F195" s="10" t="n">
+      <c r="E195" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -10532,13 +10562,13 @@
           <t>Construction</t>
         </is>
       </c>
-      <c r="D196" s="8" t="n">
+      <c r="D196" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E196" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F196" s="10" t="n">
+      <c r="E196" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F196" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -10558,13 +10588,13 @@
           <t>Education and Training</t>
         </is>
       </c>
-      <c r="D197" s="8" t="n">
+      <c r="D197" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E197" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F197" s="10" t="n">
+      <c r="E197" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -10584,13 +10614,13 @@
           <t>Government/Public Administration</t>
         </is>
       </c>
-      <c r="D198" s="8" t="n">
+      <c r="D198" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E198" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F198" s="10" t="n">
+      <c r="E198" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -10610,13 +10640,13 @@
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="D199" s="8" t="n">
+      <c r="D199" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E199" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F199" s="10" t="n">
+      <c r="E199" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -10636,13 +10666,13 @@
           <t>Sports/Entertainment/Gambling</t>
         </is>
       </c>
-      <c r="D200" s="8" t="n">
+      <c r="D200" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E200" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F200" s="10" t="n">
+      <c r="E200" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F200" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -10662,13 +10692,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D201" s="8" t="n">
+      <c r="D201" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E201" s="8" t="n">
+      <c r="E201" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="F201" s="10" t="n">
+      <c r="F201" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10686,13 +10716,13 @@
           <t>Missing</t>
         </is>
       </c>
-      <c r="D202" s="8" t="n">
+      <c r="D202" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E202" s="8" t="n">
+      <c r="E202" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="F202" s="10" t="n">
+      <c r="F202" s="13" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -10710,13 +10740,13 @@
           <t>ACTION PLANT PAY</t>
         </is>
       </c>
-      <c r="D203" s="8" t="n">
+      <c r="D203" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E203" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F203" s="10" t="n">
+      <c r="E203" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F203" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -10734,13 +10764,13 @@
           <t>AMCOVA PTY LTD</t>
         </is>
       </c>
-      <c r="D204" s="8" t="n">
+      <c r="D204" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E204" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F204" s="10" t="n">
+      <c r="E204" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10758,13 +10788,13 @@
           <t>ANDREA SABEYm fleeton</t>
         </is>
       </c>
-      <c r="D205" s="8" t="n">
+      <c r="D205" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E205" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F205" s="10" t="n">
+      <c r="E205" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10782,13 +10812,13 @@
           <t>BEST &amp; LESS PTY</t>
         </is>
       </c>
-      <c r="D206" s="8" t="n">
+      <c r="D206" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E206" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F206" s="10" t="n">
+      <c r="E206" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10806,13 +10836,13 @@
           <t>BIBRA LAKE TYREP PAYROLL</t>
         </is>
       </c>
-      <c r="D207" s="8" t="n">
+      <c r="D207" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E207" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F207" s="10" t="n">
+      <c r="E207" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10830,13 +10860,13 @@
           <t>BNE Catholic Edu</t>
         </is>
       </c>
-      <c r="D208" s="8" t="n">
+      <c r="D208" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E208" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F208" s="10" t="n">
+      <c r="E208" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10854,13 +10884,13 @@
           <t>CBA NetBank READ BROS PTY LTD</t>
         </is>
       </c>
-      <c r="D209" s="8" t="n">
+      <c r="D209" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E209" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F209" s="10" t="n">
+      <c r="E209" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10878,13 +10908,13 @@
           <t>CROWN MELBOURNE BWK 2026B08</t>
         </is>
       </c>
-      <c r="D210" s="8" t="n">
+      <c r="D210" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E210" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F210" s="10" t="n">
+      <c r="E210" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F210" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -10902,13 +10932,13 @@
           <t>FBIS INTERNATION FBIS</t>
         </is>
       </c>
-      <c r="D211" s="8" t="n">
+      <c r="D211" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E211" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F211" s="10" t="n">
+      <c r="E211" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10926,13 +10956,13 @@
           <t>GO AHEAD GROUP H</t>
         </is>
       </c>
-      <c r="D212" s="8" t="n">
+      <c r="D212" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E212" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F212" s="10" t="n">
+      <c r="E212" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F212" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -10950,13 +10980,13 @@
           <t>JBS AUSTRALIA PT</t>
         </is>
       </c>
-      <c r="D213" s="8" t="n">
+      <c r="D213" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E213" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F213" s="10" t="n">
+      <c r="E213" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F213" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10974,13 +11004,13 @@
           <t>JC COURIERS JC COURIERS</t>
         </is>
       </c>
-      <c r="D214" s="8" t="n">
+      <c r="D214" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E214" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F214" s="10" t="n">
+      <c r="E214" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F214" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -10998,13 +11028,13 @@
           <t>JD Sports Fashio Payroll</t>
         </is>
       </c>
-      <c r="D215" s="8" t="n">
+      <c r="D215" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E215" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F215" s="10" t="n">
+      <c r="E215" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11022,13 +11052,13 @@
           <t>MCPEAKE FACILITY</t>
         </is>
       </c>
-      <c r="D216" s="8" t="n">
+      <c r="D216" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E216" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F216" s="10" t="n">
+      <c r="E216" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11046,13 +11076,13 @@
           <t>MGM Bulk Pty Ltd</t>
         </is>
       </c>
-      <c r="D217" s="8" t="n">
+      <c r="D217" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E217" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F217" s="10" t="n">
+      <c r="E217" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F217" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -11070,13 +11100,13 @@
           <t>Mount St Benedic &amp;</t>
         </is>
       </c>
-      <c r="D218" s="8" t="n">
+      <c r="D218" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E218" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F218" s="10" t="n">
+      <c r="E218" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F218" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -11094,13 +11124,13 @@
           <t>PETBARN PTY LIMI</t>
         </is>
       </c>
-      <c r="D219" s="8" t="n">
+      <c r="D219" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E219" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F219" s="10" t="n">
+      <c r="E219" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F219" s="13" t="n">
         <v>0.02777777777777778</v>
       </c>
     </row>
@@ -11118,13 +11148,13 @@
           <t>Pay Van Homes Sales</t>
         </is>
       </c>
-      <c r="D220" s="8" t="n">
+      <c r="D220" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E220" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F220" s="10" t="n">
+      <c r="E220" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11142,13 +11172,13 @@
           <t>S A RELF &amp; SONS</t>
         </is>
       </c>
-      <c r="D221" s="8" t="n">
+      <c r="D221" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E221" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F221" s="10" t="n">
+      <c r="E221" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F221" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11166,13 +11196,13 @@
           <t>Others</t>
         </is>
       </c>
-      <c r="D222" s="8" t="n">
+      <c r="D222" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E222" s="8" t="n">
+      <c r="E222" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F222" s="10" t="n">
+      <c r="F222" s="13" t="n">
         <v>0.05555555555555555</v>
       </c>
     </row>
@@ -11190,13 +11220,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D223" s="8" t="n">
+      <c r="D223" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="E223" s="8" t="n">
+      <c r="E223" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="F223" s="10" t="n">
+      <c r="F223" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11214,13 +11244,13 @@
           <t>Missing</t>
         </is>
       </c>
-      <c r="D224" s="8" t="n">
+      <c r="D224" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E224" s="8" t="n">
+      <c r="E224" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="F224" s="10" t="n">
+      <c r="F224" s="13" t="n">
         <v>0.775</v>
       </c>
     </row>
@@ -11238,13 +11268,13 @@
           <t>ACTION PLANT PAY</t>
         </is>
       </c>
-      <c r="D225" s="8" t="n">
+      <c r="D225" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E225" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F225" s="10" t="n">
+      <c r="E225" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11262,13 +11292,13 @@
           <t>AMCOVA PTY LTD</t>
         </is>
       </c>
-      <c r="D226" s="8" t="n">
+      <c r="D226" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E226" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F226" s="10" t="n">
+      <c r="E226" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11286,13 +11316,13 @@
           <t>ANDREA SABEYm fleeton</t>
         </is>
       </c>
-      <c r="D227" s="8" t="n">
+      <c r="D227" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E227" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F227" s="10" t="n">
+      <c r="E227" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F227" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -11310,13 +11340,13 @@
           <t>BEST &amp; LESS PTY</t>
         </is>
       </c>
-      <c r="D228" s="8" t="n">
+      <c r="D228" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E228" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F228" s="10" t="n">
+      <c r="E228" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F228" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11334,13 +11364,13 @@
           <t>BIBRA LAKE TYREP PAYROLL</t>
         </is>
       </c>
-      <c r="D229" s="8" t="n">
+      <c r="D229" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E229" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F229" s="10" t="n">
+      <c r="E229" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F229" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -11358,13 +11388,13 @@
           <t>BNE Catholic Edu</t>
         </is>
       </c>
-      <c r="D230" s="8" t="n">
+      <c r="D230" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E230" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F230" s="10" t="n">
+      <c r="E230" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F230" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -11382,13 +11412,13 @@
           <t>CBA NetBank READ BROS PTY LTD</t>
         </is>
       </c>
-      <c r="D231" s="8" t="n">
+      <c r="D231" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E231" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F231" s="10" t="n">
+      <c r="E231" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F231" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -11406,13 +11436,13 @@
           <t>CROWN MELBOURNE BWK 2026B08</t>
         </is>
       </c>
-      <c r="D232" s="8" t="n">
+      <c r="D232" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E232" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F232" s="10" t="n">
+      <c r="E232" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F232" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11430,13 +11460,13 @@
           <t>FBIS INTERNATION FBIS</t>
         </is>
       </c>
-      <c r="D233" s="8" t="n">
+      <c r="D233" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E233" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F233" s="10" t="n">
+      <c r="E233" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F233" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -11454,13 +11484,13 @@
           <t>GO AHEAD GROUP H</t>
         </is>
       </c>
-      <c r="D234" s="8" t="n">
+      <c r="D234" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E234" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F234" s="10" t="n">
+      <c r="E234" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F234" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11478,13 +11508,13 @@
           <t>JBS AUSTRALIA PT</t>
         </is>
       </c>
-      <c r="D235" s="8" t="n">
+      <c r="D235" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E235" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F235" s="10" t="n">
+      <c r="E235" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F235" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -11502,13 +11532,13 @@
           <t>JC COURIERS JC COURIERS</t>
         </is>
       </c>
-      <c r="D236" s="8" t="n">
+      <c r="D236" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E236" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F236" s="10" t="n">
+      <c r="E236" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11526,13 +11556,13 @@
           <t>JD Sports Fashio Payroll</t>
         </is>
       </c>
-      <c r="D237" s="8" t="n">
+      <c r="D237" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E237" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F237" s="10" t="n">
+      <c r="E237" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F237" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -11550,13 +11580,13 @@
           <t>MCPEAKE FACILITY</t>
         </is>
       </c>
-      <c r="D238" s="8" t="n">
+      <c r="D238" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E238" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F238" s="10" t="n">
+      <c r="E238" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F238" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11574,13 +11604,13 @@
           <t>MGM Bulk Pty Ltd</t>
         </is>
       </c>
-      <c r="D239" s="8" t="n">
+      <c r="D239" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E239" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F239" s="10" t="n">
+      <c r="E239" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F239" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11598,13 +11628,13 @@
           <t>Mount St Benedic &amp;</t>
         </is>
       </c>
-      <c r="D240" s="8" t="n">
+      <c r="D240" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E240" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F240" s="10" t="n">
+      <c r="E240" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11622,13 +11652,13 @@
           <t>PETBARN PTY LIMI</t>
         </is>
       </c>
-      <c r="D241" s="8" t="n">
+      <c r="D241" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E241" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F241" s="10" t="n">
+      <c r="E241" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F241" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11646,13 +11676,13 @@
           <t>Pay Van Homes Sales</t>
         </is>
       </c>
-      <c r="D242" s="8" t="n">
+      <c r="D242" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E242" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F242" s="10" t="n">
+      <c r="E242" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F242" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -11670,13 +11700,13 @@
           <t>S A RELF &amp; SONS</t>
         </is>
       </c>
-      <c r="D243" s="8" t="n">
+      <c r="D243" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E243" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F243" s="10" t="n">
+      <c r="E243" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F243" s="13" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -11694,13 +11724,13 @@
           <t>Others</t>
         </is>
       </c>
-      <c r="D244" s="8" t="n">
+      <c r="D244" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E244" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F244" s="10" t="n">
+      <c r="E244" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F244" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11718,13 +11748,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D245" s="8" t="n">
+      <c r="D245" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="E245" s="8" t="n">
+      <c r="E245" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="F245" s="10" t="n">
+      <c r="F245" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11742,13 +11772,13 @@
           <t>Missing</t>
         </is>
       </c>
-      <c r="D246" s="8" t="n">
+      <c r="D246" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E246" s="8" t="n">
+      <c r="E246" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="F246" s="10" t="n">
+      <c r="F246" s="13" t="n">
         <v>0.7826086956521739</v>
       </c>
     </row>
@@ -11766,13 +11796,13 @@
           <t>ACTION PLANT PAY</t>
         </is>
       </c>
-      <c r="D247" s="8" t="n">
+      <c r="D247" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E247" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F247" s="10" t="n">
+      <c r="E247" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11790,13 +11820,13 @@
           <t>AMCOVA PTY LTD</t>
         </is>
       </c>
-      <c r="D248" s="8" t="n">
+      <c r="D248" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E248" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F248" s="10" t="n">
+      <c r="E248" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F248" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
     </row>
@@ -11814,13 +11844,13 @@
           <t>ANDREA SABEYm fleeton</t>
         </is>
       </c>
-      <c r="D249" s="8" t="n">
+      <c r="D249" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E249" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F249" s="10" t="n">
+      <c r="E249" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F249" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11838,13 +11868,13 @@
           <t>BEST &amp; LESS PTY</t>
         </is>
       </c>
-      <c r="D250" s="8" t="n">
+      <c r="D250" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E250" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F250" s="10" t="n">
+      <c r="E250" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F250" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
     </row>
@@ -11862,13 +11892,13 @@
           <t>BIBRA LAKE TYREP PAYROLL</t>
         </is>
       </c>
-      <c r="D251" s="8" t="n">
+      <c r="D251" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E251" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F251" s="10" t="n">
+      <c r="E251" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F251" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11886,13 +11916,13 @@
           <t>BNE Catholic Edu</t>
         </is>
       </c>
-      <c r="D252" s="8" t="n">
+      <c r="D252" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E252" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F252" s="10" t="n">
+      <c r="E252" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F252" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11910,13 +11940,13 @@
           <t>CBA NetBank READ BROS PTY LTD</t>
         </is>
       </c>
-      <c r="D253" s="8" t="n">
+      <c r="D253" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E253" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F253" s="10" t="n">
+      <c r="E253" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11934,13 +11964,13 @@
           <t>CROWN MELBOURNE BWK 2026B08</t>
         </is>
       </c>
-      <c r="D254" s="8" t="n">
+      <c r="D254" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E254" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F254" s="10" t="n">
+      <c r="E254" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11958,13 +11988,13 @@
           <t>FBIS INTERNATION FBIS</t>
         </is>
       </c>
-      <c r="D255" s="8" t="n">
+      <c r="D255" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E255" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F255" s="10" t="n">
+      <c r="E255" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F255" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11982,13 +12012,13 @@
           <t>GO AHEAD GROUP H</t>
         </is>
       </c>
-      <c r="D256" s="8" t="n">
+      <c r="D256" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E256" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F256" s="10" t="n">
+      <c r="E256" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F256" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12006,13 +12036,13 @@
           <t>JBS AUSTRALIA PT</t>
         </is>
       </c>
-      <c r="D257" s="8" t="n">
+      <c r="D257" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E257" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F257" s="10" t="n">
+      <c r="E257" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F257" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12030,13 +12060,13 @@
           <t>JC COURIERS JC COURIERS</t>
         </is>
       </c>
-      <c r="D258" s="8" t="n">
+      <c r="D258" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E258" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F258" s="10" t="n">
+      <c r="E258" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F258" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12054,13 +12084,13 @@
           <t>JD Sports Fashio Payroll</t>
         </is>
       </c>
-      <c r="D259" s="8" t="n">
+      <c r="D259" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E259" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F259" s="10" t="n">
+      <c r="E259" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F259" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12078,13 +12108,13 @@
           <t>MCPEAKE FACILITY</t>
         </is>
       </c>
-      <c r="D260" s="8" t="n">
+      <c r="D260" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E260" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F260" s="10" t="n">
+      <c r="E260" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F260" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
     </row>
@@ -12102,13 +12132,13 @@
           <t>MGM Bulk Pty Ltd</t>
         </is>
       </c>
-      <c r="D261" s="8" t="n">
+      <c r="D261" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E261" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F261" s="10" t="n">
+      <c r="E261" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F261" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12126,13 +12156,13 @@
           <t>Mount St Benedic &amp;</t>
         </is>
       </c>
-      <c r="D262" s="8" t="n">
+      <c r="D262" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E262" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F262" s="10" t="n">
+      <c r="E262" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12150,13 +12180,13 @@
           <t>PETBARN PTY LIMI</t>
         </is>
       </c>
-      <c r="D263" s="8" t="n">
+      <c r="D263" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E263" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F263" s="10" t="n">
+      <c r="E263" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F263" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12174,13 +12204,13 @@
           <t>Pay Van Homes Sales</t>
         </is>
       </c>
-      <c r="D264" s="8" t="n">
+      <c r="D264" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E264" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F264" s="10" t="n">
+      <c r="E264" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F264" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12198,13 +12228,13 @@
           <t>S A RELF &amp; SONS</t>
         </is>
       </c>
-      <c r="D265" s="8" t="n">
+      <c r="D265" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E265" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F265" s="10" t="n">
+      <c r="E265" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F265" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12222,13 +12252,13 @@
           <t>Others</t>
         </is>
       </c>
-      <c r="D266" s="8" t="n">
+      <c r="D266" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E266" s="8" t="n">
+      <c r="E266" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F266" s="10" t="n">
+      <c r="F266" s="13" t="n">
         <v>0.08695652173913043</v>
       </c>
     </row>
@@ -12246,13 +12276,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D267" s="8" t="n">
+      <c r="D267" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="E267" s="8" t="n">
+      <c r="E267" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="F267" s="10" t="n">
+      <c r="F267" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12272,13 +12302,13 @@
           <t>Missing</t>
         </is>
       </c>
-      <c r="D268" s="8" t="n">
+      <c r="D268" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E268" s="8" t="n">
+      <c r="E268" s="10" t="n">
         <v>76</v>
       </c>
-      <c r="F268" s="10" t="n">
+      <c r="F268" s="13" t="n">
         <v>0.7676767676767676</v>
       </c>
     </row>
@@ -12298,13 +12328,13 @@
           <t>ACTION PLANT PAY</t>
         </is>
       </c>
-      <c r="D269" s="8" t="n">
+      <c r="D269" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E269" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F269" s="10" t="n">
+      <c r="E269" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F269" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -12324,13 +12354,13 @@
           <t>AMCOVA PTY LTD</t>
         </is>
       </c>
-      <c r="D270" s="8" t="n">
+      <c r="D270" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E270" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F270" s="10" t="n">
+      <c r="E270" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F270" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -12350,13 +12380,13 @@
           <t>ANDREA SABEYm fleeton</t>
         </is>
       </c>
-      <c r="D271" s="8" t="n">
+      <c r="D271" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E271" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F271" s="10" t="n">
+      <c r="E271" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F271" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -12376,13 +12406,13 @@
           <t>BEST &amp; LESS PTY</t>
         </is>
       </c>
-      <c r="D272" s="8" t="n">
+      <c r="D272" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E272" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F272" s="10" t="n">
+      <c r="E272" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F272" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -12402,13 +12432,13 @@
           <t>BIBRA LAKE TYREP PAYROLL</t>
         </is>
       </c>
-      <c r="D273" s="8" t="n">
+      <c r="D273" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E273" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F273" s="10" t="n">
+      <c r="E273" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F273" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -12428,13 +12458,13 @@
           <t>BNE Catholic Edu</t>
         </is>
       </c>
-      <c r="D274" s="8" t="n">
+      <c r="D274" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E274" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F274" s="10" t="n">
+      <c r="E274" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F274" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -12454,13 +12484,13 @@
           <t>CBA NetBank READ BROS PTY LTD</t>
         </is>
       </c>
-      <c r="D275" s="8" t="n">
+      <c r="D275" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E275" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F275" s="10" t="n">
+      <c r="E275" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F275" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -12480,13 +12510,13 @@
           <t>CROWN MELBOURNE BWK 2026B08</t>
         </is>
       </c>
-      <c r="D276" s="8" t="n">
+      <c r="D276" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E276" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F276" s="10" t="n">
+      <c r="E276" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F276" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -12506,13 +12536,13 @@
           <t>FBIS INTERNATION FBIS</t>
         </is>
       </c>
-      <c r="D277" s="8" t="n">
+      <c r="D277" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E277" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F277" s="10" t="n">
+      <c r="E277" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F277" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -12532,13 +12562,13 @@
           <t>GO AHEAD GROUP H</t>
         </is>
       </c>
-      <c r="D278" s="8" t="n">
+      <c r="D278" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E278" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F278" s="10" t="n">
+      <c r="E278" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F278" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -12558,13 +12588,13 @@
           <t>JBS AUSTRALIA PT</t>
         </is>
       </c>
-      <c r="D279" s="8" t="n">
+      <c r="D279" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E279" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F279" s="10" t="n">
+      <c r="E279" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F279" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -12584,13 +12614,13 @@
           <t>JC COURIERS JC COURIERS</t>
         </is>
       </c>
-      <c r="D280" s="8" t="n">
+      <c r="D280" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E280" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F280" s="10" t="n">
+      <c r="E280" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F280" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -12610,13 +12640,13 @@
           <t>JD Sports Fashio Payroll</t>
         </is>
       </c>
-      <c r="D281" s="8" t="n">
+      <c r="D281" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E281" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F281" s="10" t="n">
+      <c r="E281" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F281" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -12636,13 +12666,13 @@
           <t>MCPEAKE FACILITY</t>
         </is>
       </c>
-      <c r="D282" s="8" t="n">
+      <c r="D282" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E282" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F282" s="10" t="n">
+      <c r="E282" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F282" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -12662,13 +12692,13 @@
           <t>MGM Bulk Pty Ltd</t>
         </is>
       </c>
-      <c r="D283" s="8" t="n">
+      <c r="D283" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E283" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F283" s="10" t="n">
+      <c r="E283" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F283" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -12688,13 +12718,13 @@
           <t>Mount St Benedic &amp;</t>
         </is>
       </c>
-      <c r="D284" s="8" t="n">
+      <c r="D284" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E284" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F284" s="10" t="n">
+      <c r="E284" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F284" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -12714,13 +12744,13 @@
           <t>PETBARN PTY LIMI</t>
         </is>
       </c>
-      <c r="D285" s="8" t="n">
+      <c r="D285" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E285" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F285" s="10" t="n">
+      <c r="E285" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F285" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -12740,13 +12770,13 @@
           <t>Pay Van Homes Sales</t>
         </is>
       </c>
-      <c r="D286" s="8" t="n">
+      <c r="D286" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E286" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F286" s="10" t="n">
+      <c r="E286" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F286" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -12766,13 +12796,13 @@
           <t>S A RELF &amp; SONS</t>
         </is>
       </c>
-      <c r="D287" s="8" t="n">
+      <c r="D287" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E287" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F287" s="10" t="n">
+      <c r="E287" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F287" s="13" t="n">
         <v>0.0101010101010101</v>
       </c>
     </row>
@@ -12792,13 +12822,13 @@
           <t>Others</t>
         </is>
       </c>
-      <c r="D288" s="8" t="n">
+      <c r="D288" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E288" s="8" t="n">
+      <c r="E288" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="F288" s="10" t="n">
+      <c r="F288" s="13" t="n">
         <v>0.04040404040404041</v>
       </c>
     </row>
@@ -12818,13 +12848,13 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D289" s="8" t="n">
+      <c r="D289" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="E289" s="8" t="n">
+      <c r="E289" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="F289" s="10" t="n">
+      <c r="F289" s="13" t="n">
         <v>1</v>
       </c>
     </row>
